--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
   <si>
     <t>#</t>
   </si>
@@ -354,6 +354,15 @@
   </si>
   <si>
     <t>Серивис мониторинга и агрегации аномалий в отзывах о товарах/услугах с определением эмоциональной окраски</t>
+  </si>
+  <si>
+    <t>Бронирование аудиторий и переговорок в университете</t>
+  </si>
+  <si>
+    <t>Сборщики - rollup</t>
+  </si>
+  <si>
+    <t>Смарт-контракты и децентрализованные приложения: устройство и принцип работы.</t>
   </si>
 </sst>
 </file>
@@ -489,12 +498,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -675,802 +681,658 @@
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="39.88671875" customWidth="1"/>
+    <col min="5" max="5" width="80.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
     <col min="8" max="8" width="106.44140625" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="17" customWidth="1"/>
-    <col min="10" max="18" width="22.44140625" style="17" customWidth="1"/>
-    <col min="19" max="19" width="33.21875" style="17" customWidth="1"/>
-    <col min="20" max="20" width="28.6640625" style="17" customWidth="1"/>
-    <col min="21" max="31" width="22.44140625" style="17" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" style="16" customWidth="1"/>
+    <col min="10" max="18" width="22.44140625" style="16" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" style="16" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" style="16" customWidth="1"/>
+    <col min="21" max="31" width="22.44140625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="21" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:31" s="20" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="X1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Y1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AA1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AD1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="AE1" s="16" t="s">
+      <c r="AE1" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
       <c r="G10">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
       <c r="G11">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L14" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17">
+      <c r="H17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19">
         <v>3</v>
       </c>
-      <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17">
-        <v>6</v>
-      </c>
-      <c r="H17" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="H19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
         <v>14</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19">
-        <v>7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>11</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20">
-        <v>7</v>
-      </c>
-      <c r="H20" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="E23" t="s">
         <v>91</v>
-      </c>
-      <c r="G21">
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD21" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22">
-        <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>81</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1478,421 +1340,542 @@
       <c r="H23" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="I23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD23" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>35</v>
       </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24">
-        <v>9</v>
-      </c>
-      <c r="H24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25">
-        <v>6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25">
-        <v>9</v>
-      </c>
-      <c r="H25" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>42</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
-      </c>
-      <c r="H26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27">
-        <v>10</v>
-      </c>
-      <c r="H27" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>6</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28">
-        <v>10</v>
-      </c>
-      <c r="H28" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
-        <v>44</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="10">
-        <v>11</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10">
-        <v>11</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
-        <v>45</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="10">
-        <v>11</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10">
-        <v>11</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="G31">
+        <v>12</v>
+      </c>
+      <c r="H31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32">
         <v>5</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
+      <c r="H32" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>12</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>15</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>17</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>21</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="G36">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D42">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42">
+        <v>12</v>
+      </c>
+      <c r="H42" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="G43">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="9">
+        <v>11</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="9">
+        <v>11</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>107</v>
+      </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
       <c r="K45" s="17"/>
@@ -1917,25 +1900,28 @@
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
     </row>
-    <row r="46" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>43</v>
-      </c>
-      <c r="B46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46">
-        <v>17</v>
-      </c>
-      <c r="E46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
+    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="9">
+        <v>11</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="9">
+        <v>11</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>107</v>
+      </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
@@ -1960,47 +1946,47 @@
       <c r="AD46" s="17"/>
       <c r="AE46" s="17"/>
     </row>
-    <row r="47" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="9">
         <v>18</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
+      <c r="AA47" s="17"/>
+      <c r="AB47" s="17"/>
+      <c r="AC47" s="17"/>
+      <c r="AD47" s="17"/>
+      <c r="AE47" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE47">
-      <sortCondition ref="G1"/>
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2021,67 +2007,67 @@
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="39.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="15" style="9" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="28.33203125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="7" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="23.21875" style="7" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="7" customWidth="1"/>
-    <col min="18" max="18" width="18.109375" style="7" customWidth="1"/>
-    <col min="19" max="19" width="35.6640625" style="7" customWidth="1"/>
-    <col min="20" max="20" width="36.88671875" style="7" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="7" customWidth="1"/>
-    <col min="22" max="22" width="18.21875" style="7" customWidth="1"/>
-    <col min="23" max="23" width="18.33203125" style="7" customWidth="1"/>
-    <col min="24" max="24" width="21.109375" style="7" customWidth="1"/>
-    <col min="25" max="25" width="19.109375" style="7" customWidth="1"/>
-    <col min="26" max="26" width="21.33203125" style="7" customWidth="1"/>
-    <col min="27" max="27" width="19.21875" style="7" customWidth="1"/>
-    <col min="28" max="16384" width="12.6640625" style="7"/>
+    <col min="5" max="5" width="80.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="15" style="8" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="28.33203125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="23.21875" style="6" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" style="6" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="6" customWidth="1"/>
+    <col min="19" max="19" width="35.6640625" style="6" customWidth="1"/>
+    <col min="20" max="20" width="36.88671875" style="6" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" style="6" customWidth="1"/>
+    <col min="22" max="22" width="18.21875" style="6" customWidth="1"/>
+    <col min="23" max="23" width="18.33203125" style="6" customWidth="1"/>
+    <col min="24" max="24" width="21.109375" style="6" customWidth="1"/>
+    <col min="25" max="25" width="19.109375" style="6" customWidth="1"/>
+    <col min="26" max="26" width="21.33203125" style="6" customWidth="1"/>
+    <col min="27" max="27" width="19.21875" style="6" customWidth="1"/>
+    <col min="28" max="16384" width="12.6640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="4">
+      <c r="F1" s="3">
         <v>46298</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1" s="4">
         <v>46312</v>
       </c>
-      <c r="H1" s="5">
+      <c r="H1" s="4">
         <v>46326</v>
       </c>
-      <c r="I1" s="5">
+      <c r="I1" s="4">
         <v>46340</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="4">
         <v>46354</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="4">
         <v>46368</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2101,7 +2087,7 @@
       <c r="E2" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2121,201 +2107,228 @@
       <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="9">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="9">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" s="9">
+        <v>79</v>
+      </c>
+      <c r="H6" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="9">
+        <v>79</v>
+      </c>
+      <c r="H7" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="9">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="H8" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="8">
         <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="9">
-        <v>6</v>
+        <v>81</v>
+      </c>
+      <c r="G11" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="9">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="9">
-        <v>6</v>
+        <v>83</v>
+      </c>
+      <c r="I14" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2334,592 +2347,596 @@
       <c r="E15" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
       <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="12">
+        <v>84</v>
+      </c>
+      <c r="I16" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17">
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="8">
         <v>4</v>
-      </c>
-      <c r="E17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="12">
-        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="12">
-        <v>3</v>
+        <v>88</v>
+      </c>
+      <c r="I18" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8">
+        <v>3</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>44</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="9">
         <v>11</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="11"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="9">
-        <v>5</v>
+      <c r="E21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="9">
-        <v>5</v>
+      <c r="A22" s="9">
+        <v>45</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="9">
+        <v>11</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>17</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>18</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="9">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="H25" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>20</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="H26" s="9">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="I26" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>21</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
-      </c>
-      <c r="I28" s="9">
+        <v>92</v>
+      </c>
+      <c r="H28" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>24</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30" s="9">
-        <v>4</v>
+        <v>93</v>
+      </c>
+      <c r="H30" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="9">
-        <v>4</v>
+        <v>93</v>
+      </c>
+      <c r="H31" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="9">
-        <v>5</v>
+        <v>94</v>
+      </c>
+      <c r="I32" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>29</v>
+      <c r="A33" s="9">
+        <v>46</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9">
+        <v>18</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J33" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D34">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+      <c r="J34" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" s="9">
+        <v>112</v>
+      </c>
+      <c r="J35" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D36">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>112</v>
+      </c>
+      <c r="J36" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s">
-        <v>41</v>
+        <v>1</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39">
-        <v>8</v>
-      </c>
-      <c r="E39" t="s">
-        <v>84</v>
-      </c>
-      <c r="I39" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>90</v>
-      </c>
-      <c r="H40" s="9">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="E41" t="s">
-        <v>82</v>
-      </c>
-      <c r="I41" s="9">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>82</v>
-      </c>
-      <c r="I43" s="9">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D44">
-        <v>17</v>
-      </c>
-      <c r="E44" t="s">
-        <v>94</v>
-      </c>
-      <c r="I44" s="9">
-        <v>6</v>
-      </c>
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>86</v>
+      <c r="A45">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="1">
-        <v>11</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J45" s="9">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>95</v>
+      <c r="A46">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="1">
-        <v>11</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9">
-        <v>1</v>
-      </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="1">
-        <v>18</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9">
-        <v>2</v>
-      </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
-      <c r="U47" s="9"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="9"/>
-      <c r="X47" s="9"/>
-      <c r="Y47" s="9"/>
-      <c r="Z47" s="9"/>
-      <c r="AA47" s="9"/>
-      <c r="AB47" s="9"/>
-      <c r="AC47" s="9"/>
-      <c r="AD47" s="9"/>
-      <c r="AE47" s="9"/>
+      <c r="A47">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8"/>
+      <c r="S47" s="8"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="8"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="8"/>
+      <c r="X47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AB47" s="8"/>
+      <c r="AC47" s="8"/>
+      <c r="AD47" s="8"/>
+      <c r="AE47" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K47">
-      <sortCondition ref="G1"/>
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>Смарт-контракты и децентрализованные приложения: устройство и принцип работы.</t>
+  </si>
+  <si>
+    <t>Чинь Тхи Тху Хоай</t>
   </si>
 </sst>
 </file>
@@ -674,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -1983,6 +1986,43 @@
       <c r="AD47" s="17"/>
       <c r="AE47" s="17"/>
     </row>
+    <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="9">
+        <v>19</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
+      <c r="AA48" s="17"/>
+      <c r="AB48" s="17"/>
+      <c r="AC48" s="17"/>
+      <c r="AD48" s="17"/>
+      <c r="AE48" s="17"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE47">
@@ -2000,7 +2040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -2736,31 +2776,29 @@
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>30</v>
-      </c>
-      <c r="B35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35">
-        <v>20</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
+      <c r="A35" s="9">
+        <v>47</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="J35" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -2777,21 +2815,30 @@
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -2799,10 +2846,10 @@
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>6</v>
@@ -2810,21 +2857,21 @@
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>18</v>
@@ -2832,10 +2879,10 @@
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>18</v>
@@ -2843,10 +2890,10 @@
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -2854,21 +2901,21 @@
     </row>
     <row r="44" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>29</v>
-      </c>
-      <c r="B44" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -2876,10 +2923,10 @@
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -2896,10 +2943,10 @@
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -2933,9 +2980,20 @@
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
     </row>
+    <row r="48" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1">
-    <sortState ref="A2:K47">
+    <sortState ref="A2:K48">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -2153,190 +2153,190 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="8">
         <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="8">
         <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="11">
+        <v>89</v>
+      </c>
+      <c r="G6" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="11">
-        <v>3</v>
+        <v>78</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="11">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="8">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="H9" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="8">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="H10" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="8">
+        <v>80</v>
+      </c>
+      <c r="H11" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="H12" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2353,30 +2353,30 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -2393,50 +2393,50 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I16" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I17" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2453,30 +2453,30 @@
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="8">
-        <v>3</v>
+        <v>88</v>
+      </c>
+      <c r="I19" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2488,41 +2488,41 @@
         <v>85</v>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="8">
-        <v>3</v>
-      </c>
+      <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="J20" s="8">
+        <v>5</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>44</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="9">
-        <v>11</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>87</v>
+      <c r="A21">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
       </c>
       <c r="J21" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>6</v>
@@ -2538,23 +2538,23 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>36</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="8">
-        <v>4</v>
+      <c r="A23" s="9">
+        <v>45</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="9">
+        <v>11</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2994,7 +2994,7 @@
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K48">
-      <sortCondition ref="D1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>Чинь Тхи Тху Хоай</t>
+  </si>
+  <si>
+    <t>Веб-сервис для создания и управления персональными базами знаний с семантическим поиском</t>
   </si>
 </sst>
 </file>
@@ -792,127 +795,235 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+      <c r="H2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>96</v>
@@ -929,25 +1040,25 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
       <c r="H9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>96</v>
@@ -964,141 +1075,102 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="G10">
         <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>79</v>
-      </c>
       <c r="G11">
-        <v>6</v>
-      </c>
-      <c r="H11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12">
+        <v>29</v>
+      </c>
+      <c r="G12">
         <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12">
-        <v>7</v>
-      </c>
-      <c r="H12" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>96</v>
@@ -1115,25 +1187,25 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>96</v>
@@ -1150,192 +1222,267 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="H19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD21" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>25</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>103</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>27</v>
+      <c r="B22" t="s">
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1355,198 +1502,225 @@
       <c r="L23" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="AD23" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D24">
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26">
+        <v>9</v>
+      </c>
+      <c r="H26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="H27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>44</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="9">
+        <v>11</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9">
+        <v>11</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>45</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="9">
+        <v>11</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9">
+        <v>11</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B31" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25">
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31">
         <v>19</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E31" t="s">
         <v>111</v>
-      </c>
-      <c r="G25">
-        <v>12</v>
-      </c>
-      <c r="H25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26">
-        <v>8</v>
-      </c>
-      <c r="H26" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
-        <v>112</v>
       </c>
       <c r="G31">
         <v>12</v>
@@ -1555,436 +1729,359 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D33">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
       <c r="G33">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="H33" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A35" s="9">
+        <v>46</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9">
+        <v>18</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9">
+        <v>13</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G36">
-        <v>9</v>
-      </c>
-      <c r="H36" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-      <c r="H38" t="s">
-        <v>100</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>45</v>
+        <v>17</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
-      </c>
-      <c r="H39" t="s">
-        <v>100</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L39" s="16" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>46</v>
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
-      </c>
-      <c r="G42">
-        <v>12</v>
-      </c>
-      <c r="H42" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43">
-        <v>9</v>
-      </c>
-      <c r="H43" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+    </row>
+    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+    </row>
+    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44">
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47">
         <v>17</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E47" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
-        <v>44</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="9">
-        <v>11</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G45" s="9">
-        <v>11</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
-      <c r="AA45" s="17"/>
-      <c r="AB45" s="17"/>
-      <c r="AC45" s="17"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="17"/>
-    </row>
-    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
-        <v>45</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="9">
-        <v>11</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G46" s="9">
-        <v>11</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="17"/>
-      <c r="AA46" s="17"/>
-      <c r="AB46" s="17"/>
-      <c r="AC46" s="17"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="17"/>
-    </row>
-    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
-        <v>46</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="9">
-        <v>18</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="17"/>
-      <c r="AA47" s="17"/>
-      <c r="AB47" s="17"/>
-      <c r="AC47" s="17"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="17"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
     </row>
     <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
@@ -2025,8 +2122,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
-    <sortState ref="A2:AE47">
-      <sortCondition ref="A1"/>
+    <sortState ref="A2:AE48">
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2113,19 +2210,19 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G2" s="8">
         <v>1</v>
@@ -2133,19 +2230,19 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
@@ -2153,19 +2250,19 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G4" s="8">
         <v>2</v>
@@ -2173,42 +2270,42 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="8">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="J5" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="8">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="J6" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -504,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -555,6 +555,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -827,6 +830,18 @@
       <c r="L2" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -862,6 +877,18 @@
       <c r="L3" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -897,6 +924,18 @@
       <c r="L4" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -932,6 +971,18 @@
       <c r="L5" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -967,6 +1018,18 @@
       <c r="L6" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1002,6 +1065,18 @@
       <c r="L7" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1037,6 +1112,18 @@
       <c r="L8" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1072,6 +1159,18 @@
       <c r="L9" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1149,6 +1248,18 @@
       <c r="L13" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -1184,6 +1295,18 @@
       <c r="L14" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -1219,6 +1342,18 @@
       <c r="L15" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -1254,6 +1389,18 @@
       <c r="L16" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
@@ -1289,6 +1436,18 @@
       <c r="L17" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -1324,6 +1483,18 @@
       <c r="L18" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -1359,6 +1530,18 @@
       <c r="L19" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -1394,6 +1577,18 @@
       <c r="L20" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -1429,6 +1624,18 @@
       <c r="L21" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>96</v>
+      </c>
       <c r="AD21" s="16" t="s">
         <v>96</v>
       </c>
@@ -1467,6 +1674,18 @@
       <c r="L22" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1502,6 +1721,18 @@
       <c r="L23" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="M23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -1588,6 +1819,18 @@
       <c r="H27" t="s">
         <v>108</v>
       </c>
+      <c r="M27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1610,6 +1853,18 @@
       </c>
       <c r="H28" t="s">
         <v>108</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
@@ -1775,8 +2030,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1785,18 +2040,45 @@
       <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>7</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>13</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+      <c r="V34" s="21"/>
+      <c r="W34" s="21"/>
+      <c r="X34" s="21"/>
+      <c r="Y34" s="21"/>
+      <c r="Z34" s="21"/>
+      <c r="AA34" s="21"/>
+      <c r="AB34" s="21"/>
+      <c r="AC34" s="21"/>
+      <c r="AD34" s="21"/>
+      <c r="AE34" s="21"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
@@ -1823,8 +2105,12 @@
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="M35" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>96</v>
+      </c>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="Q35" s="17"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>Веб-сервис для создания и управления персональными базами знаний с семантическим поиском</t>
+  </si>
+  <si>
+    <t>нужны правки</t>
   </si>
 </sst>
 </file>
@@ -504,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -558,6 +561,15 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,10 +701,10 @@
     <col min="1" max="1" width="5.21875" customWidth="1"/>
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" style="22" customWidth="1"/>
     <col min="5" max="5" width="80.88671875" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="22.88671875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" style="22" customWidth="1"/>
     <col min="8" max="8" width="106.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" style="16" customWidth="1"/>
     <col min="10" max="18" width="22.44140625" style="16" customWidth="1"/>
@@ -798,21 +810,21 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2">
-        <v>15</v>
+      <c r="D2" s="22">
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2">
+        <v>77</v>
+      </c>
+      <c r="G2" s="22">
         <v>1</v>
       </c>
       <c r="H2" t="s">
@@ -845,25 +857,25 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>15</v>
+      <c r="D3" s="22">
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>77</v>
+      </c>
+      <c r="G3" s="22">
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>96</v>
@@ -892,25 +904,25 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="D4" s="22">
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="G4" s="22">
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>96</v>
@@ -939,25 +951,25 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="22">
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>99</v>
+        <v>78</v>
+      </c>
+      <c r="G5" s="22">
+        <v>3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>96</v>
@@ -986,25 +998,25 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D6" s="22">
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>99</v>
+        <v>79</v>
+      </c>
+      <c r="G6" s="22">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>101</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>96</v>
@@ -1033,25 +1045,25 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D7" s="22">
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
+        <v>79</v>
+      </c>
+      <c r="G7" s="22">
+        <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>96</v>
@@ -1080,25 +1092,25 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D8" s="22">
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="G8" s="22">
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>96</v>
@@ -1127,25 +1139,25 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D9" s="22">
+        <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="G9" s="22">
+        <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>96</v>
@@ -1174,114 +1186,171 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="22">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10">
-        <v>4</v>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="22">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D11" s="22">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="22">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G12">
-        <v>4</v>
+      <c r="D12" s="22">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="22">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13">
-        <v>13</v>
+      <c r="D13" s="22">
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="G13" s="22">
+        <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D14" s="22">
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="G14" s="22">
+        <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>96</v>
@@ -1309,73 +1378,77 @@
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
+      <c r="A15" s="1">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="8">
         <v>13</v>
       </c>
-      <c r="E15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P15" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="H15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="21"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="22">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
       <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
+        <v>84</v>
+      </c>
+      <c r="G16" s="22">
+        <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I16" s="16" t="s">
         <v>96</v>
@@ -1404,25 +1477,25 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
+        <v>29</v>
+      </c>
+      <c r="D17" s="22">
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17">
-        <v>6</v>
-      </c>
-      <c r="H17" t="s">
-        <v>101</v>
+        <v>88</v>
+      </c>
+      <c r="G17" s="22">
+        <v>2</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>96</v>
@@ -1451,25 +1524,25 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18">
-        <v>7</v>
+        <v>29</v>
+      </c>
+      <c r="D18" s="22">
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>104</v>
+        <v>88</v>
+      </c>
+      <c r="G18" s="22">
+        <v>2</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>96</v>
@@ -1498,619 +1571,613 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D19" s="22">
+        <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19">
-        <v>7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="22">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>44</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="10">
         <v>11</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20">
-        <v>7</v>
-      </c>
-      <c r="H20" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21">
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD21" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="E21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="24"/>
+      <c r="G21" s="10">
+        <v>11</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22">
-        <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P22" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="A22" s="9">
+        <v>45</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="10">
+        <v>11</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="24"/>
+      <c r="G22" s="10">
+        <v>11</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D23">
-        <v>5</v>
+      <c r="D23" s="22">
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P23" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G24">
-        <v>9</v>
+      <c r="D24" s="22">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="22">
+        <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>100</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D25">
-        <v>6</v>
+      <c r="D25" s="22">
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="G25" s="22">
+        <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>109</v>
+        <v>100</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D26">
-        <v>6</v>
+      <c r="D26" s="22">
+        <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
+        <v>91</v>
+      </c>
+      <c r="G26" s="22">
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD26" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
+        <v>29</v>
+      </c>
+      <c r="D27" s="22">
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27">
-        <v>10</v>
-      </c>
-      <c r="H27" t="s">
-        <v>108</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P27" s="16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28">
+        <v>18</v>
+      </c>
+      <c r="D28" s="22">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="22">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="22">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="22">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="22">
         <v>16</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E30" t="s">
         <v>93</v>
       </c>
-      <c r="G28">
+      <c r="G30" s="22">
         <v>10</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H30" t="s">
         <v>108</v>
       </c>
-      <c r="M28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>44</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="9">
-        <v>11</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9">
-        <v>11</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="17"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>45</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="9">
-        <v>11</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9">
-        <v>11</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="17"/>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="17"/>
+      <c r="M30" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="D31" s="22">
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31">
-        <v>12</v>
+        <v>93</v>
+      </c>
+      <c r="G31" s="22">
+        <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P31" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D32">
-        <v>20</v>
+      <c r="D32" s="22">
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>46</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10">
+        <v>18</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="24"/>
+      <c r="G33" s="10">
+        <v>13</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="17"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+    </row>
+    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="22">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="20"/>
+      <c r="G34" s="22">
         <v>12</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H34" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33">
-        <v>12</v>
-      </c>
-      <c r="H33" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>4</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="1">
-        <v>7</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" s="1">
-        <v>13</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N34" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="21"/>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="21"/>
-      <c r="W34" s="21"/>
-      <c r="X34" s="21"/>
-      <c r="Y34" s="21"/>
-      <c r="Z34" s="21"/>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="21"/>
-      <c r="AD34" s="21"/>
-      <c r="AE34" s="21"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="9">
-        <v>18</v>
+      <c r="D35" s="10">
+        <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9">
-        <v>13</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>114</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F35" s="24"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9"/>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
-      <c r="M35" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>96</v>
-      </c>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="Q35" s="17"/>
@@ -2131,133 +2198,156 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D36" s="22">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="22">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="22">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="22">
         <v>12</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>18</v>
+      <c r="H37" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="G38" s="22">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="G39" s="22">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="G40" s="22">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D41">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>85</v>
+      <c r="G41" s="22">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>35</v>
+        <v>5</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>29</v>
-      </c>
-      <c r="B43" t="s">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>34</v>
-      </c>
-      <c r="B44" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>36</v>
-      </c>
-      <c r="B45" t="s">
-        <v>43</v>
+        <v>17</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45">
-        <v>12</v>
-      </c>
-      <c r="E45" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45"/>
-      <c r="G45"/>
+        <v>18</v>
+      </c>
+      <c r="D45" s="22"/>
+      <c r="E45"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="22"/>
       <c r="H45"/>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
@@ -2285,22 +2375,18 @@
     </row>
     <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>39</v>
-      </c>
-      <c r="B46" t="s">
-        <v>46</v>
+        <v>21</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>85</v>
-      </c>
-      <c r="F46"/>
-      <c r="G46"/>
+        <v>18</v>
+      </c>
+      <c r="D46" s="22"/>
+      <c r="E46"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="22"/>
       <c r="H46"/>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
@@ -2328,22 +2414,18 @@
     </row>
     <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D47">
-        <v>17</v>
-      </c>
-      <c r="E47" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47"/>
-      <c r="G47"/>
+      <c r="D47" s="22"/>
+      <c r="E47"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="22"/>
       <c r="H47"/>
       <c r="I47" s="16"/>
       <c r="J47" s="16"/>
@@ -2370,46 +2452,48 @@
       <c r="AE47" s="16"/>
     </row>
     <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
-        <v>47</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D48" s="9">
-        <v>19</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="17"/>
-      <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="17"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="17"/>
-      <c r="AA48" s="17"/>
-      <c r="AB48" s="17"/>
-      <c r="AC48" s="17"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="17"/>
+      <c r="A48">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="22"/>
+      <c r="E48"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="22"/>
+      <c r="H48"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE48">
-      <sortCondition ref="G1"/>
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2429,7 +2513,7 @@
     <col min="1" max="1" width="5.21875" customWidth="1"/>
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="28" style="22" customWidth="1"/>
     <col min="5" max="5" width="80.88671875" customWidth="1"/>
     <col min="6" max="6" width="14.109375" style="8" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="8" customWidth="1"/>
@@ -2504,7 +2588,7 @@
       <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="22">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -2524,7 +2608,7 @@
       <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="22">
         <v>5</v>
       </c>
       <c r="E3" t="s">
@@ -2544,7 +2628,7 @@
       <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="22">
         <v>12</v>
       </c>
       <c r="E4" t="s">
@@ -2564,7 +2648,7 @@
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="22">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -2584,7 +2668,7 @@
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="22">
         <v>1</v>
       </c>
       <c r="E6" t="s">
@@ -2604,7 +2688,7 @@
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="22">
         <v>2</v>
       </c>
       <c r="E7" t="s">
@@ -2624,7 +2708,7 @@
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="22">
         <v>2</v>
       </c>
       <c r="E8" t="s">
@@ -2644,7 +2728,7 @@
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="22">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -2664,7 +2748,7 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="22">
         <v>3</v>
       </c>
       <c r="E10" t="s">
@@ -2684,7 +2768,7 @@
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="22">
         <v>4</v>
       </c>
       <c r="E11" t="s">
@@ -2704,7 +2788,7 @@
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="22">
         <v>4</v>
       </c>
       <c r="E12" t="s">
@@ -2724,7 +2808,7 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="22">
         <v>6</v>
       </c>
       <c r="E13" t="s">
@@ -2744,7 +2828,7 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="22">
         <v>6</v>
       </c>
       <c r="E14" t="s">
@@ -2764,7 +2848,7 @@
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="22">
         <v>7</v>
       </c>
       <c r="E15" t="s">
@@ -2784,7 +2868,7 @@
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="22">
         <v>7</v>
       </c>
       <c r="E16" t="s">
@@ -2804,7 +2888,7 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="22">
         <v>8</v>
       </c>
       <c r="E17" t="s">
@@ -2824,7 +2908,7 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="22">
         <v>9</v>
       </c>
       <c r="E18" t="s">
@@ -2844,7 +2928,7 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="22">
         <v>9</v>
       </c>
       <c r="E19" t="s">
@@ -2864,7 +2948,7 @@
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="22">
         <v>10</v>
       </c>
       <c r="E20" t="s">
@@ -2890,7 +2974,7 @@
       <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="22">
         <v>10</v>
       </c>
       <c r="E21" t="s">
@@ -2910,7 +2994,7 @@
       <c r="C22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="10">
         <v>11</v>
       </c>
       <c r="E22" s="9" t="s">
@@ -2930,7 +3014,7 @@
       <c r="C23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="10">
         <v>11</v>
       </c>
       <c r="E23" s="9" t="s">
@@ -2950,7 +3034,7 @@
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="22">
         <v>13</v>
       </c>
       <c r="E24" t="s">
@@ -2970,7 +3054,7 @@
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="22">
         <v>13</v>
       </c>
       <c r="E25" t="s">
@@ -2990,7 +3074,7 @@
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="22">
         <v>14</v>
       </c>
       <c r="E26" t="s">
@@ -3010,7 +3094,7 @@
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="22">
         <v>14</v>
       </c>
       <c r="E27" t="s">
@@ -3030,7 +3114,7 @@
       <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="22">
         <v>15</v>
       </c>
       <c r="E28" t="s">
@@ -3050,7 +3134,7 @@
       <c r="C29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="22">
         <v>15</v>
       </c>
       <c r="E29" t="s">
@@ -3070,7 +3154,7 @@
       <c r="C30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="22">
         <v>16</v>
       </c>
       <c r="E30" t="s">
@@ -3090,7 +3174,7 @@
       <c r="C31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="22">
         <v>16</v>
       </c>
       <c r="E31" t="s">
@@ -3110,7 +3194,7 @@
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="22">
         <v>17</v>
       </c>
       <c r="E32" t="s">
@@ -3128,7 +3212,7 @@
         <v>97</v>
       </c>
       <c r="C33" s="9"/>
-      <c r="D33" s="9">
+      <c r="D33" s="10">
         <v>18</v>
       </c>
       <c r="E33" s="9" t="s">
@@ -3148,7 +3232,7 @@
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="22">
         <v>19</v>
       </c>
       <c r="E34" t="s">
@@ -3166,7 +3250,7 @@
         <v>113</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="9">
+      <c r="D35" s="10">
         <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
@@ -3186,7 +3270,7 @@
       <c r="C36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="22">
         <v>20</v>
       </c>
       <c r="E36" t="s">
@@ -3206,7 +3290,7 @@
       <c r="C37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="22">
         <v>20</v>
       </c>
       <c r="E37" t="s">
@@ -3314,7 +3398,7 @@
       <c r="C46" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D46"/>
+      <c r="D46" s="22"/>
       <c r="E46"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -3334,7 +3418,7 @@
       <c r="C47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D47"/>
+      <c r="D47" s="22"/>
       <c r="E47"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>нужны правки</t>
+  </si>
+  <si>
+    <t>веб-приложение для быстрого оповещения жителей дома об авариях</t>
   </si>
 </sst>
 </file>
@@ -857,25 +860,25 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="22">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="22">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="22">
-        <v>3</v>
-      </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>96</v>
@@ -904,25 +907,25 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="22">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G4" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>96</v>
@@ -951,25 +954,25 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D5" s="22">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="22">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="22">
-        <v>3</v>
-      </c>
-      <c r="H5" t="s">
-        <v>103</v>
+      <c r="H5" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>96</v>
@@ -998,25 +1001,25 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D6" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G6" s="22">
-        <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>96</v>
@@ -1045,25 +1048,25 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" s="22">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="22">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="22">
-        <v>6</v>
-      </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>96</v>
@@ -1092,25 +1095,25 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G8" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>96</v>
@@ -1139,25 +1142,25 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D9" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G9" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>96</v>
@@ -1186,171 +1189,114 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="22">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="G10" s="22">
-        <v>8</v>
-      </c>
-      <c r="H10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="22">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="G11" s="22">
-        <v>8</v>
-      </c>
-      <c r="H11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="22">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>82</v>
-      </c>
       <c r="G12" s="22">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G13" s="22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>109</v>
+        <v>100</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D14" s="22">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G14" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>96</v>
@@ -1378,77 +1324,73 @@
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
+      <c r="A15">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="8">
+        <v>29</v>
+      </c>
+      <c r="D15" s="22">
         <v>13</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N15" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="22">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16" s="22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G16" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" s="16" t="s">
         <v>96</v>
@@ -1477,25 +1419,25 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D17" s="22">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" s="22">
-        <v>2</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>99</v>
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>101</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>96</v>
@@ -1524,25 +1466,25 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D18" s="22">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G18" s="22">
-        <v>2</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>99</v>
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>96</v>
@@ -1571,346 +1513,367 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D19" s="22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="G19" s="22">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D20" s="22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="G20" s="22">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>44</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="10">
-        <v>11</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="10">
-        <v>11</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="17"/>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17"/>
-      <c r="AC21" s="17"/>
-      <c r="AD21" s="17"/>
-      <c r="AE21" s="17"/>
+      <c r="A21">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="22">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="22">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>45</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="10">
-        <v>11</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="10">
-        <v>11</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="17"/>
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="22">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>115</v>
+        <v>91</v>
+      </c>
+      <c r="G23" s="22">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD23" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="22">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G24" s="22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H24" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P24" s="16" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="22">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G25" s="22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P25" s="16" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="22">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>91</v>
-      </c>
       <c r="G26" s="22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD26" s="16" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D27" s="22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="G27" s="22">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>108</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D28" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" s="22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>96</v>
@@ -1926,258 +1889,250 @@
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>14</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="22">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" s="22">
-        <v>1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P29" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="A29" s="9">
+        <v>44</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="10">
+        <v>11</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="24"/>
+      <c r="G29" s="10">
+        <v>11</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="22">
-        <v>16</v>
-      </c>
-      <c r="E30" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="22">
-        <v>10</v>
-      </c>
-      <c r="H30" t="s">
-        <v>108</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N30" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O30" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P30" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="A30" s="9">
+        <v>45</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="10">
+        <v>11</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="24"/>
+      <c r="G30" s="10">
+        <v>11</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D31" s="22">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="G31" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H31" t="s">
-        <v>108</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N31" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O31" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P31" s="16" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="22">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>112</v>
+      </c>
+      <c r="G32" s="22">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
-        <v>46</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10">
-        <v>18</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F33" s="24"/>
-      <c r="G33" s="10">
+      <c r="A33">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="22">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="22">
+        <v>12</v>
+      </c>
+      <c r="H33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="8">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="8">
         <v>13</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="17"/>
-      <c r="AB33" s="17"/>
-      <c r="AC33" s="17"/>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="17"/>
-    </row>
-    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>24</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="22">
-        <v>19</v>
-      </c>
-      <c r="E34" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="22">
-        <v>12</v>
-      </c>
-      <c r="H34" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+      <c r="V34" s="21"/>
+      <c r="W34" s="21"/>
+      <c r="X34" s="21"/>
+      <c r="Y34" s="21"/>
+      <c r="Z34" s="21"/>
+      <c r="AA34" s="21"/>
+      <c r="AB34" s="21"/>
+      <c r="AC34" s="21"/>
+      <c r="AD34" s="21"/>
+      <c r="AE34" s="21"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F35" s="24"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="9"/>
+      <c r="G35" s="10">
+        <v>13</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="M35" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>96</v>
+      </c>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="Q35" s="17"/>
@@ -2198,108 +2153,144 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="B36" t="s">
-        <v>37</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G36" s="22">
-        <v>12</v>
-      </c>
-      <c r="H36" t="s">
-        <v>110</v>
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D37" s="22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G37" s="22">
-        <v>12</v>
-      </c>
-      <c r="H37" t="s">
-        <v>110</v>
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="22">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D38" s="22">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>2</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="22">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D39" s="22">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="22">
-        <v>4</v>
+      <c r="D40" s="22">
+        <v>17</v>
+      </c>
+      <c r="E40" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G41" s="22">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s">
-        <v>109</v>
-      </c>
+      <c r="A41" s="9">
+        <v>47</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10">
+        <v>19</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" s="24"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17"/>
+      <c r="AB41" s="17"/>
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
@@ -2493,7 +2484,7 @@
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE48">
-      <sortCondition ref="D1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2580,608 +2571,608 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D2" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="8">
+        <v>78</v>
+      </c>
+      <c r="H2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D3" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="8">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D4" s="22">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="8">
+        <v>80</v>
+      </c>
+      <c r="H4" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D5" s="22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="8">
-        <v>6</v>
+        <v>80</v>
+      </c>
+      <c r="H5" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D6" s="22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" s="8">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D7" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="H7" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D8" s="22">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H8" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="22">
         <v>13</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="22">
-        <v>3</v>
-      </c>
       <c r="E9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="11">
-        <v>3</v>
+        <v>90</v>
+      </c>
+      <c r="H9" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="22">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="22">
-        <v>3</v>
-      </c>
       <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="11">
-        <v>3</v>
+        <v>92</v>
+      </c>
+      <c r="H10" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D11" s="22">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="11">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="H11" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="22">
         <v>16</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="22">
-        <v>4</v>
-      </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H12" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D13" s="22">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="8">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="H13" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="8">
+        <v>81</v>
+      </c>
+      <c r="G14" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D15" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
-      </c>
-      <c r="I15" s="8">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="22">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="22">
-        <v>7</v>
-      </c>
       <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="I16" s="8">
+        <v>89</v>
+      </c>
+      <c r="G16" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D17" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="8">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="J17" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18" s="8">
-        <v>4</v>
+        <v>77</v>
+      </c>
+      <c r="J18" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I19" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8">
-        <v>5</v>
-      </c>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D21" s="22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
-      </c>
-      <c r="J21" s="8">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="I21" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="22">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="10">
-        <v>11</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>45</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="10">
-        <v>11</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="8">
-        <v>1</v>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="22">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="22">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="8">
+        <v>88</v>
+      </c>
+      <c r="I24" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="22">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="8">
+        <v>88</v>
+      </c>
+      <c r="I25" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="22">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="8">
+        <v>85</v>
+      </c>
+      <c r="J26" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="22">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="8">
+        <v>85</v>
+      </c>
+      <c r="J27" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="22">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>92</v>
-      </c>
-      <c r="H28" s="8">
-        <v>5</v>
+      <c r="A28" s="9">
+        <v>44</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="10">
+        <v>11</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>14</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="22">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="8">
-        <v>5</v>
+      <c r="A29" s="9">
+        <v>45</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="10">
+        <v>11</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D30" s="22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" s="8">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="I30" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D31" s="22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="8">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="I31" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3461,7 +3452,7 @@
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K48">
-      <sortCondition ref="G1"/>
+      <sortCondition ref="H1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -813,19 +813,19 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="22">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G2" s="22">
         <v>1</v>
@@ -860,10 +860,10 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -907,25 +907,25 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D4" s="22">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G4" s="22">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>105</v>
+        <v>2</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>96</v>
@@ -954,10 +954,10 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1001,25 +1001,25 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D6" s="22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G6" s="22">
-        <v>2</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>99</v>
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>103</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>96</v>
@@ -1048,19 +1048,19 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="22">
         <v>3</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -1142,57 +1142,24 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="22">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="G9" s="22">
-        <v>3</v>
-      </c>
-      <c r="H9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
@@ -1203,13 +1170,13 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G11" s="22">
         <v>4</v>
@@ -1217,33 +1184,66 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D12" s="22">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>84</v>
+      </c>
       <c r="G12" s="22">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="22">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G13" s="22">
         <v>5</v>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1325,25 +1325,25 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D15" s="22">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>96</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -1419,25 +1419,25 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>96</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -1513,19 +1513,19 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G19" s="22">
         <v>7</v>
@@ -1560,25 +1560,28 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D20" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="G20" s="22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I20" s="16" t="s">
         <v>96</v>
@@ -1607,10 +1610,10 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -1657,22 +1660,19 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="22">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="G22" s="22">
         <v>8</v>
@@ -1704,63 +1704,39 @@
       <c r="P22" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="AD22" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="22">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G23" s="22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD23" s="16" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -1780,19 +1756,13 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
         <v>42</v>
       </c>
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D25" s="22">
-        <v>6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>82</v>
       </c>
       <c r="G25" s="22">
         <v>9</v>
@@ -1803,27 +1773,45 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="D26" s="22">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
       </c>
       <c r="G26" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1854,46 +1842,58 @@
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>6</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" s="9">
+        <v>44</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="10">
         <v>11</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="22">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="22">
-        <v>10</v>
-      </c>
-      <c r="H28" t="s">
-        <v>108</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="E28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="24"/>
+      <c r="G28" s="10">
+        <v>11</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>6</v>
@@ -1936,67 +1936,43 @@
       <c r="AE29" s="17"/>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>45</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="10">
-        <v>11</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="24"/>
-      <c r="G30" s="10">
-        <v>11</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="17"/>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="17"/>
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="22">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="22">
+        <v>12</v>
+      </c>
+      <c r="H30" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D31" s="22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G31" s="22">
         <v>12</v>
@@ -2007,10 +1983,10 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2029,134 +2005,134 @@
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>48</v>
+      <c r="A33" s="1">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="22">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="22">
-        <v>12</v>
-      </c>
-      <c r="H33" t="s">
-        <v>110</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D33" s="8">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="8">
+        <v>13</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="21"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="21"/>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="21"/>
+      <c r="AE33" s="21"/>
     </row>
     <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>4</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="8">
-        <v>7</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="8">
+      <c r="A34" s="9">
+        <v>46</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10">
+        <v>18</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="24"/>
+      <c r="G34" s="10">
         <v>13</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N34" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="21"/>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="21"/>
-      <c r="W34" s="21"/>
-      <c r="X34" s="21"/>
-      <c r="Y34" s="21"/>
-      <c r="Z34" s="21"/>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="21"/>
-      <c r="AD34" s="21"/>
-      <c r="AE34" s="21"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="17"/>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
-        <v>46</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10">
-        <v>18</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F35" s="24"/>
-      <c r="G35" s="10">
-        <v>13</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
+      <c r="A35">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="22">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="22">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -2176,25 +2152,19 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D37" s="22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
-      </c>
-      <c r="G37" s="22">
-        <v>14</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
@@ -2571,70 +2541,70 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D2" s="22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="8">
+        <v>81</v>
+      </c>
+      <c r="G2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D3" s="22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="8">
+        <v>81</v>
+      </c>
+      <c r="G3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D4" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" s="11">
+        <v>89</v>
+      </c>
+      <c r="G4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -2645,36 +2615,36 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="8">
-        <v>2</v>
+      <c r="H5" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="11">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -2686,35 +2656,35 @@
         <v>79</v>
       </c>
       <c r="H7" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D8" s="22">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="8">
-        <v>4</v>
+        <v>79</v>
+      </c>
+      <c r="H8" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2726,35 +2696,35 @@
         <v>90</v>
       </c>
       <c r="H9" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="22">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="22">
-        <v>15</v>
-      </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H10" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -2766,35 +2736,35 @@
         <v>92</v>
       </c>
       <c r="H11" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D12" s="22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H12" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
@@ -2806,150 +2776,150 @@
         <v>93</v>
       </c>
       <c r="H13" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D14" s="22">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="8">
         <v>5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="8">
+        <v>82</v>
+      </c>
+      <c r="I15" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="8">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D17" s="22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="J17" s="8">
-        <v>6</v>
+        <v>83</v>
+      </c>
+      <c r="I17" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D18" s="22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="8">
-        <v>6</v>
+        <v>83</v>
+      </c>
+      <c r="I18" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I19" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -2957,150 +2927,150 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="22">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="8">
         <v>4</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="22">
-        <v>7</v>
-      </c>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="8">
-        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>7</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D22" s="22">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I22" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="22">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I23" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="22">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I24" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>27</v>
-      </c>
-      <c r="B25" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D25" s="22">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I25" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D26" s="22">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
-      </c>
-      <c r="J26" s="8">
-        <v>5</v>
+        <v>78</v>
+      </c>
+      <c r="I26" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>39</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="22">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>85</v>
+      <c r="A27" s="9">
+        <v>44</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="10">
+        <v>11</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="J27" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>6</v>
@@ -3117,178 +3087,178 @@
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C29" s="9"/>
       <c r="D29" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J29" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="22">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
-      </c>
-      <c r="I30" s="8">
-        <v>5</v>
+        <v>111</v>
+      </c>
+      <c r="J30" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="22">
-        <v>14</v>
-      </c>
-      <c r="E31" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="8">
-        <v>5</v>
+      <c r="A31" s="9">
+        <v>47</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10">
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J31" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="22">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="8">
-        <v>6</v>
+        <v>112</v>
+      </c>
+      <c r="J32" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
-        <v>46</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10">
-        <v>18</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>98</v>
+      <c r="A33">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="22">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
       </c>
       <c r="J33" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="22">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="J34" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
-        <v>47</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10">
-        <v>19</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>111</v>
+      <c r="A35">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="22">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
       </c>
       <c r="J35" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>30</v>
-      </c>
-      <c r="B36" t="s">
-        <v>37</v>
+        <v>16</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D36" s="22">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="J36" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>41</v>
-      </c>
-      <c r="B37" t="s">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D37" s="22">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="J37" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3452,7 +3422,7 @@
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K48">
-      <sortCondition ref="H1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D9" s="22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H9" s="8">
         <v>3</v>
@@ -2701,19 +2701,19 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D10" s="22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="8">
         <v>3</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D11" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="8">
         <v>4</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D12" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="8">
         <v>4</v>
@@ -2761,165 +2761,165 @@
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D13" s="22">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="8">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D14" s="22">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="8">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D15" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I15" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D17" s="22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D18" s="22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I18" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I19" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -2927,338 +2927,338 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I21" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I22" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D23" s="22">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I23" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D24" s="22">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I24" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>18</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="22">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="8">
-        <v>7</v>
+      <c r="A25" s="9">
+        <v>44</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="10">
+        <v>11</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>20</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="22">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="8">
-        <v>7</v>
+      <c r="A26" s="9">
+        <v>45</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="10">
+        <v>11</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J26" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C27" s="9"/>
       <c r="D27" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J27" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
-        <v>45</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="10">
-        <v>11</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>87</v>
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="22">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
       </c>
       <c r="J28" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J29" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J30" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
-        <v>47</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10">
-        <v>19</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>111</v>
+      <c r="A31">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="22">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>112</v>
       </c>
       <c r="J31" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>37</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J32" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D33" s="22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J33" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>23</v>
-      </c>
-      <c r="B34" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D34" s="22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J34" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>39</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D35" s="22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J35" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>16</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D36" s="22">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J36" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>19</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D37" s="22">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J37" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -374,7 +374,16 @@
     <t>нужны правки</t>
   </si>
   <si>
-    <t>веб-приложение для быстрого оповещения жителей дома об авариях</t>
+    <t>Нгуен Тхи Хань Хуен</t>
+  </si>
+  <si>
+    <t>CI/CD: принципы построения и автоматизации</t>
+  </si>
+  <si>
+    <t>Веб-приложение для быстрого оповещения жителей дома об авариях</t>
+  </si>
+  <si>
+    <t>Веб-приложение для интернет-магазина одежды</t>
   </si>
 </sst>
 </file>
@@ -698,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -813,272 +822,150 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="22">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="G2" s="22">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P2" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="22">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="G3" s="22">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D4" s="22">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="22">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="22">
-        <v>2</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P4" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="22">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="22">
-        <v>2</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>96</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D5" s="8">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="8">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="22">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="22">
-        <v>3</v>
-      </c>
-      <c r="H6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P6" s="16" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D7" s="22">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G7" s="22">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>96</v>
@@ -1095,25 +982,25 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D8" s="22">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G8" s="22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>96</v>
@@ -1142,67 +1029,166 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D9" s="22">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
       <c r="G9" s="22">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="22">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="22">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="22">
-        <v>4</v>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="D11" s="22">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
       </c>
       <c r="G11" s="22">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D12" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G12" s="22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>96</v>
@@ -1231,72 +1217,36 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="22">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="22">
-        <v>5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D14" s="22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" s="22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>96</v>
@@ -1325,25 +1275,25 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D15" s="22">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G15" s="22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>96</v>
@@ -1372,593 +1322,464 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="22">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="22">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="22">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="22">
+        <v>3</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="22">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="22">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="22">
+        <v>3</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="22">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="22">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD23" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="22">
         <v>10</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="22">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="22">
-        <v>6</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P16" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="22">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="22">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="22">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="22">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="22">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="22">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="E27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="22">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="22">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="22">
+        <v>2</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="22">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="22">
-        <v>4</v>
-      </c>
-      <c r="E17" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="22">
-        <v>7</v>
-      </c>
-      <c r="H17" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P17" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>11</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="22">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="22">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P18" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="22">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="22">
-        <v>7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>25</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="22">
-        <v>5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="22">
-        <v>8</v>
-      </c>
-      <c r="H20" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>33</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="22">
-        <v>5</v>
-      </c>
-      <c r="E21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="22">
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="22">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="E29" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="22">
-        <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD22" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>40</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="22">
-        <v>6</v>
-      </c>
-      <c r="E23" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="22">
-        <v>9</v>
-      </c>
-      <c r="H23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>42</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="22">
-        <v>6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="22">
-        <v>9</v>
-      </c>
-      <c r="H24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="22">
-        <v>9</v>
-      </c>
-      <c r="H25" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="22">
-        <v>16</v>
-      </c>
-      <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="22">
-        <v>10</v>
-      </c>
-      <c r="H26" t="s">
-        <v>108</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="22">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="22">
-        <v>10</v>
-      </c>
-      <c r="H27" t="s">
-        <v>108</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P27" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
-        <v>44</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="10">
-        <v>11</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" s="24"/>
-      <c r="G28" s="10">
-        <v>11</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="17"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>45</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="10">
-        <v>11</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="10">
-        <v>11</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="17"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="22">
-        <v>19</v>
-      </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="22">
-        <v>12</v>
-      </c>
-      <c r="H30" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1981,480 +1802,615 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="22">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="G32" s="22">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>100</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P32" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="22">
         <v>4</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="8">
-        <v>7</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="8">
-        <v>13</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N33" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="21"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
-      <c r="AE33" s="21"/>
     </row>
     <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
-        <v>46</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10">
-        <v>18</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" s="24"/>
-      <c r="G34" s="10">
-        <v>13</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="17"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="17"/>
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="22">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="22">
+        <v>8</v>
+      </c>
+      <c r="H34" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D35" s="22">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>85</v>
-      </c>
-      <c r="G35" s="22">
-        <v>14</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="22">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
-        <v>85</v>
-      </c>
       <c r="G36" s="22">
-        <v>14</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>19</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D37" s="22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>89</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="22">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>115</v>
+        <v>84</v>
+      </c>
+      <c r="G38" s="22">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="G39" s="22">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="22">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>94</v>
+        <v>85</v>
+      </c>
+      <c r="G40" s="22">
+        <v>14</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10">
-        <v>19</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F41" s="24"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="17"/>
-      <c r="AA41" s="17"/>
-      <c r="AB41" s="17"/>
-      <c r="AC41" s="17"/>
-      <c r="AD41" s="17"/>
-      <c r="AE41" s="17"/>
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="22">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="22">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D42" s="22">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" s="22">
+        <v>12</v>
+      </c>
+      <c r="H42" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>12</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D43" s="22">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="22">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="22">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="10">
+        <v>11</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="24"/>
+      <c r="G45" s="10">
+        <v>11</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
+      <c r="AA45" s="17"/>
+      <c r="AB45" s="17"/>
+      <c r="AC45" s="17"/>
+      <c r="AD45" s="17"/>
+      <c r="AE45" s="17"/>
+    </row>
+    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="10">
+        <v>11</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" s="24"/>
+      <c r="G46" s="10">
+        <v>11</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
+      <c r="AA46" s="17"/>
+      <c r="AB46" s="17"/>
+      <c r="AC46" s="17"/>
+      <c r="AD46" s="17"/>
+      <c r="AE46" s="17"/>
+    </row>
+    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>46</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="10">
+        <v>18</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="24"/>
+      <c r="G47" s="10">
+        <v>13</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
+      <c r="AA47" s="17"/>
+      <c r="AB47" s="17"/>
+      <c r="AC47" s="17"/>
+      <c r="AD47" s="17"/>
+      <c r="AE47" s="17"/>
+    </row>
+    <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="10">
+        <v>19</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="24"/>
+      <c r="G48" s="10"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
+      <c r="AA48" s="17"/>
+      <c r="AB48" s="17"/>
+      <c r="AC48" s="17"/>
+      <c r="AD48" s="17"/>
+      <c r="AE48" s="17"/>
+    </row>
+    <row r="49" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="9">
+        <v>48</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="10">
+        <v>21</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="24"/>
+      <c r="G49" s="10">
         <v>15</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>17</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="22"/>
-      <c r="E45"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="22"/>
-      <c r="H45"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-      <c r="Z45" s="16"/>
-      <c r="AA45" s="16"/>
-      <c r="AB45" s="16"/>
-      <c r="AC45" s="16"/>
-      <c r="AD45" s="16"/>
-      <c r="AE45" s="16"/>
-    </row>
-    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>21</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="22"/>
-      <c r="E46"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="22"/>
-      <c r="H46"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="16"/>
-      <c r="AA46" s="16"/>
-      <c r="AB46" s="16"/>
-      <c r="AC46" s="16"/>
-      <c r="AD46" s="16"/>
-      <c r="AE46" s="16"/>
-    </row>
-    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>29</v>
-      </c>
-      <c r="B47" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="22"/>
-      <c r="E47"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="22"/>
-      <c r="H47"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
-      <c r="AC47" s="16"/>
-      <c r="AD47" s="16"/>
-      <c r="AE47" s="16"/>
-    </row>
-    <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>34</v>
-      </c>
-      <c r="B48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="22"/>
-      <c r="E48"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="22"/>
-      <c r="H48"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
-      <c r="AA48" s="16"/>
-      <c r="AB48" s="16"/>
-      <c r="AC48" s="16"/>
-      <c r="AD48" s="16"/>
-      <c r="AE48" s="16"/>
+      <c r="H49" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
+      <c r="Z49" s="17"/>
+      <c r="AA49" s="17"/>
+      <c r="AB49" s="17"/>
+      <c r="AC49" s="17"/>
+      <c r="AD49" s="17"/>
+      <c r="AE49" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
-    <sortState ref="A2:AE48">
-      <sortCondition ref="G1"/>
+    <sortState ref="A2:AE49">
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2468,7 +2424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -3262,22 +3218,31 @@
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="9">
+        <v>48</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="10">
+        <v>21</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K38" s="8">
         <v>1</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>6</v>
@@ -3285,10 +3250,10 @@
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
@@ -3296,21 +3261,21 @@
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>18</v>
@@ -3318,10 +3283,10 @@
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -3329,10 +3294,10 @@
     </row>
     <row r="44" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -3340,21 +3305,21 @@
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>29</v>
-      </c>
-      <c r="B45" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3371,10 +3336,10 @@
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3410,18 +3375,29 @@
     </row>
     <row r="48" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>35</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
-    <sortState ref="A2:K48">
+    <sortState ref="A2:K49">
       <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -822,53 +822,131 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="22">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="22">
-        <v>4</v>
+      <c r="H2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D3" s="22">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
       </c>
       <c r="G3" s="22">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D4" s="22">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G4" s="22">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>108</v>
+        <v>2</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="M4" s="16" t="s">
         <v>96</v>
@@ -884,88 +962,132 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="22">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="8">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N5" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="22">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D6" s="22">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="22">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" s="22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G7" s="22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>96</v>
@@ -982,25 +1104,25 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" s="22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G8" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>96</v>
@@ -1029,166 +1151,67 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="22">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>79</v>
-      </c>
       <c r="G9" s="22">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="22">
+      <c r="G10" s="22">
         <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="22">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="22">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="G11" s="22">
-        <v>6</v>
-      </c>
-      <c r="H11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D12" s="22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G12" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>96</v>
@@ -1217,36 +1240,72 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D13" s="22">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="22">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="22">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="22">
-        <v>15</v>
-      </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G14" s="22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>96</v>
@@ -1275,25 +1334,25 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D15" s="22">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G15" s="22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>96</v>
@@ -1322,464 +1381,593 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D16" s="22">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="22">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="22">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="22">
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="22">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="22">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="22">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="22">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="22">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="22">
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="22">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="22">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD20" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="22">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="22">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="22">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="22">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="22">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="22">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="22">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>3</v>
       </c>
-      <c r="H17" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P17" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="22">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="22">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
+        <v>108</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="22">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="22">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>108</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>44</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="10">
+        <v>11</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="24"/>
+      <c r="G28" s="10">
+        <v>11</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>45</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="10">
+        <v>11</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="24"/>
+      <c r="G29" s="10">
+        <v>11</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>24</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="22">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="22">
-        <v>3</v>
-      </c>
-      <c r="H19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="22">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="22">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="22">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="22">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>103</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="22">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="22">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD23" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="22">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="22">
-        <v>14</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="22">
-        <v>19</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G30" s="22">
         <v>12</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="22">
-        <v>5</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="22">
-        <v>8</v>
-      </c>
-      <c r="H26" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="22">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="22">
-        <v>2</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P27" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="22">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="22">
-        <v>2</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="22">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1802,587 +1990,492 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="22">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="22">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="8">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="8">
         <v>13</v>
       </c>
-      <c r="E32" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="22">
-        <v>5</v>
-      </c>
-      <c r="H32" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P32" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="22">
-        <v>4</v>
-      </c>
+      <c r="H33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="21"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="21"/>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="21"/>
+      <c r="AE33" s="21"/>
     </row>
     <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="22">
-        <v>5</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="22">
-        <v>8</v>
-      </c>
-      <c r="H34" t="s">
-        <v>102</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
+      <c r="A34" s="9">
+        <v>46</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10">
+        <v>18</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="24"/>
+      <c r="G34" s="10">
+        <v>13</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="17"/>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D35" s="22">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="22">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D36" s="22">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
       <c r="G36" s="22">
-        <v>9</v>
-      </c>
-      <c r="H36" t="s">
-        <v>109</v>
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="22">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>115</v>
-      </c>
+      <c r="A37" s="9">
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="10">
+        <v>21</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" s="24"/>
+      <c r="G37" s="10">
+        <v>15</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17"/>
+      <c r="AB37" s="17"/>
+      <c r="AC37" s="17"/>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="17"/>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="22">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="G38" s="22">
-        <v>5</v>
-      </c>
-      <c r="H38" t="s">
-        <v>100</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P38" s="16" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="22">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39" s="22">
-        <v>5</v>
-      </c>
-      <c r="H39" t="s">
-        <v>100</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="M39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="N39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="O39" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P39" s="16" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>46</v>
+        <v>15</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="22">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G40" s="22">
-        <v>14</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
+        <v>17</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="22">
-        <v>6</v>
-      </c>
-      <c r="E41" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="22">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D42" s="22">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
-      </c>
-      <c r="G42" s="22">
-        <v>12</v>
-      </c>
-      <c r="H42" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="22">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="22">
-        <v>9</v>
-      </c>
-      <c r="H43" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="22">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="22"/>
+      <c r="E45"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="22"/>
+      <c r="H45"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+    </row>
+    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="22"/>
+      <c r="E46"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="22"/>
+      <c r="H46"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+    </row>
+    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="22">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="22"/>
+      <c r="H47"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+    </row>
+    <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>43</v>
+      </c>
+      <c r="B48" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="22">
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="22">
         <v>17</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E48" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
-        <v>44</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="10">
-        <v>11</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" s="24"/>
-      <c r="G45" s="10">
-        <v>11</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
-      <c r="AA45" s="17"/>
-      <c r="AB45" s="17"/>
-      <c r="AC45" s="17"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="17"/>
-    </row>
-    <row r="46" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
-        <v>45</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="10">
-        <v>11</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F46" s="24"/>
-      <c r="G46" s="10">
-        <v>11</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="17"/>
-      <c r="AA46" s="17"/>
-      <c r="AB46" s="17"/>
-      <c r="AC46" s="17"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="17"/>
-    </row>
-    <row r="47" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
-        <v>46</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="10">
-        <v>18</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F47" s="24"/>
-      <c r="G47" s="10">
-        <v>13</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="N47" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="17"/>
-      <c r="AA47" s="17"/>
-      <c r="AB47" s="17"/>
-      <c r="AC47" s="17"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="17"/>
-    </row>
-    <row r="48" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
-        <v>47</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D48" s="10">
-        <v>19</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="10"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="17"/>
-      <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="17"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="17"/>
-      <c r="AA48" s="17"/>
-      <c r="AB48" s="17"/>
-      <c r="AC48" s="17"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="17"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="22"/>
+      <c r="H48"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
     </row>
     <row r="49" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="D49" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F49" s="24"/>
-      <c r="G49" s="10">
-        <v>15</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="G49" s="10"/>
       <c r="I49" s="17"/>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -2410,7 +2503,7 @@
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE49">
-      <sortCondition ref="A1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2557,19 +2650,19 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" s="11">
         <v>1</v>
@@ -2577,79 +2670,79 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="8">
+        <v>79</v>
+      </c>
+      <c r="H6" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" s="22">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="11">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="22">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="22">
-        <v>3</v>
-      </c>
       <c r="E8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="11">
+        <v>92</v>
+      </c>
+      <c r="H8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D9" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="8">
         <v>3</v>
@@ -2657,19 +2750,19 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D10" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="8">
         <v>3</v>
@@ -2677,205 +2770,205 @@
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D11" s="22">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="8">
-        <v>4</v>
+        <v>82</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D12" s="22">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="8">
-        <v>4</v>
+        <v>82</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D13" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I13" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D14" s="22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I14" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D15" s="22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I15" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D16" s="22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I16" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I17" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I18" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I19" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
@@ -2883,82 +2976,83 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D21" s="22">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I21" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D22" s="22">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I22" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D23" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H23" s="11"/>
       <c r="I23" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D24" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I24" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
